--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62445.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62445.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2028</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S1-01-01</t>
+          <t>S1-01-G1</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ikxluùlel</t>
+          <t>Naximc</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ETGE N IN</t>
+          <t>LQREAWE</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G02D</t>
+          <t>G02C</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62445.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62445.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G02C</t>
+          <t>G02B</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -756,6 +756,9 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
+      <c r="J9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62445.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62445.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Naximc</t>
+          <t>Haxime</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LQREAWE</t>
+          <t>ETRENUE</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>345</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -730,10 +730,10 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>4.48</v>
+        <v>4.98</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62445.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62445.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Haxime</t>
+          <t>HAXIME</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62445.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62445.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
